--- a/tool/kintone-resourse-generator/run-list/sample.xlsx
+++ b/tool/kintone-resourse-generator/run-list/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\kintone-resourse-generator\run-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EA40AB-5D34-43D7-8A50-7EDCC44E551F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F08EFB-CB56-4C93-81BA-E82A8FD85830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>スペース識別名</t>
   </si>
@@ -35,12 +35,6 @@
   </si>
   <si>
     <t>class-space</t>
-  </si>
-  <si>
-    <t>L21</t>
-  </si>
-  <si>
-    <t>L22</t>
   </si>
 </sst>
 </file>
@@ -407,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" customWidth="1"/>
@@ -437,28 +431,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
